--- a/SuppXLS/Demands/Dem_Alloc+Series.xlsx
+++ b/SuppXLS/Demands/Dem_Alloc+Series.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Veda\Veda_models\Demo_models\001_KHM_TIMES_20260606\SuppXLS\Demands\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261016\SuppXLS\Demands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DE9AB5-230B-4A58-9C4C-0775BA041226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C86532B-198A-4981-81C2-EC796084208C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
   <si>
     <t>Constant</t>
   </si>
@@ -294,12 +294,6 @@
     <t>DTMAR</t>
   </si>
   <si>
-    <t>DAMANC</t>
-  </si>
-  <si>
-    <t>DAPUMP</t>
-  </si>
-  <si>
     <t>DIBOIL</t>
   </si>
   <si>
@@ -316,6 +310,9 @@
   </si>
   <si>
     <t>DIENGN</t>
+  </si>
+  <si>
+    <t>DAOT</t>
   </si>
 </sst>
 </file>
@@ -644,7 +641,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>57151</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -869,13 +866,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1708,7 +1705,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:Q25"/>
+  <dimension ref="B2:Q24"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -1746,7 +1743,7 @@
         <v>57</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -1763,7 +1760,7 @@
         <v>57</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -1780,10 +1777,10 @@
         <v>57</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
         <v>0</v>
@@ -1797,10 +1794,10 @@
         <v>57</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>0</v>
@@ -1809,15 +1806,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>67</v>
+      <c r="C8" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>0</v>
@@ -1831,7 +1828,7 @@
         <v>57</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
         <v>66</v>
@@ -1848,7 +1845,7 @@
         <v>57</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>66</v>
@@ -1865,7 +1862,7 @@
         <v>57</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
         <v>66</v>
@@ -1882,7 +1879,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
         <v>66</v>
@@ -1899,7 +1896,7 @@
         <v>57</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
         <v>66</v>
@@ -1915,11 +1912,11 @@
       <c r="B14" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>82</v>
+      <c r="C14" t="s">
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>0</v>
@@ -1927,13 +1924,14 @@
       <c r="F14" t="s">
         <v>0</v>
       </c>
+      <c r="M14" s="9"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
         <v>65</v>
@@ -1944,17 +1942,16 @@
       <c r="F15" t="s">
         <v>0</v>
       </c>
-      <c r="M15" s="9"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>57</v>
       </c>
-      <c r="C16" t="s">
-        <v>61</v>
+      <c r="C16" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
         <v>0</v>
@@ -1967,11 +1964,11 @@
       <c r="B17" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
+      <c r="C17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>1</v>
       </c>
       <c r="E17" t="s">
         <v>0</v>
@@ -1984,11 +1981,11 @@
       <c r="B18" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>1</v>
+      <c r="C18" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="E18" t="s">
         <v>0</v>
@@ -2002,10 +1999,10 @@
         <v>57</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
         <v>0</v>
@@ -2013,16 +2010,25 @@
       <c r="F19" t="s">
         <v>0</v>
       </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>1</v>
+      <c r="C20" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="E20" t="s">
         <v>0</v>
@@ -2044,11 +2050,11 @@
       <c r="B21" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>65</v>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>66</v>
       </c>
       <c r="E21" t="s">
         <v>0</v>
@@ -2071,10 +2077,10 @@
         <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
         <v>0</v>
@@ -2097,10 +2103,10 @@
         <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
         <v>0</v>
@@ -2123,7 +2129,7 @@
         <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
         <v>66</v>
@@ -2144,32 +2150,6 @@
       <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" t="s">
-        <v>0</v>
-      </c>
-      <c r="F25" t="s">
-        <v>0</v>
-      </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
